--- a/finance-tracker-TEMPLATE.xlsx
+++ b/finance-tracker-TEMPLATE.xlsx
@@ -539,7 +539,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D29"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -599,283 +599,296 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Owner</t>
+          <t>Language</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>shown in the header; blank to hide</t>
+          <t>UI language: en, it, es, fr or de. Blank = follow the browser</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>History from</t>
+          <t>Owner</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>shown in the header; blank to hide</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>History from</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
           <t>YYYY-MM — trims the long-run charts; blank = all data</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>WEALTH GROUPS</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>groups INVESTMENTS lines into the wealth donut</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
+          <t>WEALTH GROUPS</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>groups INVESTMENTS lines into the wealth donut</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>Match (investment name contains; comma-separated)</t>
         </is>
       </c>
-      <c r="B10" s="1" t="inlineStr">
+      <c r="B11" s="1" t="inlineStr">
         <is>
           <t>Label</t>
         </is>
       </c>
-      <c r="C10" s="1" t="inlineStr">
+      <c r="C11" s="1" t="inlineStr">
         <is>
           <t>Colour</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>home,property</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Home</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>#5b9cf6</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>pension,sipp</t>
+          <t>home,property</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Pension</t>
+          <t>Home</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>#f59e0b</t>
+          <t>#5b9cf6</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>pension,sipp</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Pension</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>#f59e0b</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
           <t>company,stake,equity</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>Company / business</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>#a78bfa</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>CATEGORIES</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>pins colour and display order; omitted categories still appear</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
+          <t>CATEGORIES</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>pins colour and display order; omitted categories still appear</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="B16" s="1" t="inlineStr">
+      <c r="B17" s="1" t="inlineStr">
         <is>
           <t>Colour</t>
         </is>
       </c>
-      <c r="C16" s="1" t="inlineStr">
+      <c r="C17" s="1" t="inlineStr">
         <is>
           <t>Order</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>Example category (replace with a List 1 value)</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>#5b9cf6</t>
         </is>
       </c>
-      <c r="C17" t="n">
+      <c r="C18" t="n">
         <v>1</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>ACCOUNT GROUPS</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>role 'card repayment' = a bill that clears a card, not a purchase</t>
-        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
+          <t>ACCOUNT GROUPS</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>role 'card repayment' = a bill that clears a card, not a purchase</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
+        <is>
           <t>Match (bill name contains; comma-separated)</t>
         </is>
       </c>
-      <c r="B20" s="1" t="inlineStr">
+      <c r="B21" s="1" t="inlineStr">
         <is>
           <t>Role</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t>card,credit</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>card repayment</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
-        <is>
-          <t>THRESHOLDS</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>tune when the dashboard warns you</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
+          <t>THRESHOLDS</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>tune when the dashboard warns you</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
+        <is>
           <t>Name</t>
         </is>
       </c>
-      <c r="B24" s="1" t="inlineStr">
+      <c r="B25" s="1" t="inlineStr">
         <is>
           <t>Value</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Runway warning months</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>2</v>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>fewer months of liquid runway than this -&gt; amber</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Pace warning pct</t>
+          <t>Runway warning months</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>spend vs day-proportional budget -&gt; amber</t>
+          <t>fewer months of liquid runway than this -&gt; amber</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Pace alert pct</t>
+          <t>Pace warning pct</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-&gt; red</t>
+          <t>spend vs day-proportional budget -&gt; amber</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Insight min spend</t>
+          <t>Pace alert pct</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>40</v>
+        <v>110</v>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>ignore categories smaller than this when detecting changes</t>
+          <t>-&gt; red</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
+          <t>Insight min spend</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>40</v>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>ignore categories smaller than this when detecting changes</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
           <t>Insight min change pct</t>
         </is>
       </c>
-      <c r="B29" t="n">
+      <c r="B30" t="n">
         <v>15</v>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>only report a change bigger than this</t>
         </is>
@@ -912,7 +925,7 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
     </row>
     <row r="4">
@@ -1108,7 +1121,7 @@
         <v>0</v>
       </c>
       <c r="E21" s="3" t="n">
-        <v>52802</v>
+        <v>52803</v>
       </c>
     </row>
     <row r="22">
@@ -1129,7 +1142,7 @@
         <v>0</v>
       </c>
       <c r="E22" s="3" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
     </row>
     <row r="24">
@@ -1294,7 +1307,7 @@
         <v>46234</v>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -1321,7 +1334,7 @@
         <v>46248</v>
       </c>
       <c r="F5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H5" t="inlineStr"/>
     </row>
@@ -1556,7 +1569,7 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B4" t="n">
         <v>0</v>
